--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T13:22:01+00:00</t>
+    <t>2026-09-14T18:30:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T18:30:11+00:00</t>
+    <t>2026-09-15T08:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T08:39:16+00:00</t>
+    <t>2026-09-15T14:26:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T14:26:14+00:00</t>
+    <t>2026-09-15T15:55:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-15T15:55:26+00:00</t>
+    <t>2026-09-16T08:21:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T08:21:32+00:00</t>
+    <t>2026-09-16T12:46:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T12:46:48+00:00</t>
+    <t>2026-09-16T14:44:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-16T14:44:43+00:00</t>
+    <t>2026-09-17T07:59:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T07:59:06+00:00</t>
+    <t>2026-09-17T12:33:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-17T12:33:54+00:00</t>
+    <t>2026-09-18T07:05:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T07:05:38+00:00</t>
+    <t>2026-09-18T08:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:38:11+00:00</t>
+    <t>2026-09-18T11:05:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
+++ b/r4-ELGA-e-Medikation-main/StructureDefinition-at-elga-emed-medication-medikation.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.1</t>
+    <t>0.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T11:05:21+00:00</t>
+    <t>2026-09-18T13:55:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
